--- a/DataXlCalcNet/DataExamples/MainExamples/Workbooks/XlDemoCPYstd.xlsx
+++ b/DataXlCalcNet/DataExamples/MainExamples/Workbooks/XlDemoCPYstd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DUHad\Documents\DataXlCalcNet\DataExamples\MainExamples\Workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92CF5C90-8C48-425A-9A3D-5570645AF591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF21E160-0509-40A1-B40E-615D97DF8905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="18923" windowHeight="19928" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="18923" windowHeight="19928" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GeneralInfo" sheetId="1" r:id="rId1"/>
@@ -1788,38 +1788,38 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="str">
-        <f t="array" ref="A4:A14">_xll.CPY_0("result  =list(zip(sys.path))")</f>
+        <f t="array" ref="A4:A14">_xll.CPY_0("result  = list(zip(sys.path))")</f>
         <v>C:\Users\DUHad\Documents\DataXlCalcNet</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
-        <v>C:\Python312\Lib\site-packages\xlcalcnet\Addin\NET48\Bin</v>
+        <v>C:\Users\DUHad\Documents\DataXlCalcNet\A01_ExamplesPython\B01_GeneralUsage\C01_Setup</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
-        <v>C:\Python312\python312.zip</v>
+        <v>C:\Python314\python314.zip</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
-        <v>C:\Python312\DLLs</v>
+        <v>C:\Python314\DLLs</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
-        <v>C:\Python312\Lib</v>
+        <v>C:\Python314\Lib</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
-        <v>C:\Python312</v>
+        <v>C:\Python314</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
-        <v>C:\Python312\Lib\site-packages</v>
+        <v>C:\Python314\Lib\site-packages</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
